--- a/docs/kinela_actualizada.xlsx
+++ b/docs/kinela_actualizada.xlsx
@@ -65,7 +65,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-09T04:34:25.771Z</t>
+          <t>2026-07-09T04:43:43.582Z</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/docs/kinela_actualizada.xlsx
+++ b/docs/kinela_actualizada.xlsx
@@ -65,7 +65,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-09T04:43:43.582Z</t>
+          <t>2026-07-09T04:59:14.250Z</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/docs/kinela_actualizada.xlsx
+++ b/docs/kinela_actualizada.xlsx
@@ -65,7 +65,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-09T04:59:14.250Z</t>
+          <t>2026-07-09T14:12:31.721Z</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1581,17 +1581,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2-2 / Noruega / Penales</t>
+          <t>2-1 / Noruega / Suplementario</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2-1 / Argentina / 90 minutos</t>
+          <t>2-0 / Argentina / 90 minutos</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -3127,17 +3127,17 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Suplementario</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3174,17 +3174,17 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>90 minutos</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -3221,17 +3221,17 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Suplementario</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3268,17 +3268,17 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>90 minutos</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3315,17 +3315,17 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>90 minutos</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -3362,17 +3362,17 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Bélgica</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Suplementario</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -3409,17 +3409,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Suplementario</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3456,17 +3456,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>90 minutos</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4067,17 +4067,17 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>90 minutos</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -4114,17 +4114,17 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>España</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>90 minutos</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4161,17 +4161,17 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Suplementario</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -4208,17 +4208,17 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>90 minutos</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5383,17 +5383,17 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>90 minutos</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5430,17 +5430,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>España</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>90 minutos</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5477,17 +5477,17 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>90 minutos</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5524,17 +5524,17 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>90 minutos</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5759,17 +5759,17 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Suplementario</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5806,17 +5806,17 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>España</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Penales</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -5853,17 +5853,17 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Suplementario</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5900,17 +5900,17 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Penales</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>38</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">

--- a/docs/kinela_actualizada.xlsx
+++ b/docs/kinela_actualizada.xlsx
@@ -60,12 +60,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>open</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-09T14:12:31.721Z</t>
+          <t>2026-07-09T16:41:54.931Z</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/docs/kinela_actualizada.xlsx
+++ b/docs/kinela_actualizada.xlsx
@@ -60,12 +60,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>closed</t>
+          <t>finished</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-09T16:41:54.931Z</t>
+          <t>2026-07-09T22:57:46.781Z</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -75,7 +75,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>86</t>
         </is>
       </c>
     </row>
@@ -161,42 +161,42 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -218,42 +218,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -265,52 +265,52 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P005</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jorge</t>
+          <t>Jesús</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -322,17 +322,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P016</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Gabriela</t>
+          <t>Anny</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -342,17 +342,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -362,12 +362,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -379,17 +379,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P006</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jesús</t>
+          <t>Diego</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -399,17 +399,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -419,12 +419,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -436,17 +436,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Anny</t>
+          <t>Gabriela</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -456,17 +456,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -476,12 +476,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -493,34 +493,34 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Diego</t>
+          <t>Jorge</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>0</t>
@@ -528,12 +528,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -550,17 +550,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aldo</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -570,17 +570,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -590,12 +590,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -607,37 +607,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Arthur</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -647,12 +647,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -664,17 +664,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P009</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Javier</t>
+          <t>Gino</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -704,12 +704,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>P007</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gino</t>
+          <t>Aldo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -741,14 +741,14 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>0</t>
@@ -761,7 +761,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -778,52 +778,52 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Javier</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>47</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -835,22 +835,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Juan</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -892,17 +892,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P017</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Arthur</t>
+          <t>Moisés</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -912,17 +912,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P022</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Óscar</t>
+          <t>Juan</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -984,12 +984,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1006,17 +1006,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P012</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1026,17 +1026,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P022</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Moisés</t>
+          <t>Óscar</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1083,19 +1083,19 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1120,17 +1120,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>P020</t>
+          <t>P012</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1489,22 +1489,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>90 minutos</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1529,12 +1529,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["Arthur"]</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>131</t>
         </is>
       </c>
     </row>
@@ -1826,17 +1826,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -2014,17 +2014,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -2202,17 +2202,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -2578,17 +2578,17 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -2766,17 +2766,17 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2964,7 +2964,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -3142,17 +3142,17 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -3330,17 +3330,17 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -3894,17 +3894,17 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -4082,17 +4082,17 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -4646,17 +4646,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -4834,17 +4834,17 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -5022,17 +5022,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -5398,17 +5398,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -5774,17 +5774,17 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>86</t>
         </is>
       </c>
     </row>
@@ -6188,7 +6188,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>131</t>
         </is>
       </c>
     </row>

--- a/docs/kinela_actualizada.xlsx
+++ b/docs/kinela_actualizada.xlsx
@@ -65,7 +65,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-09T22:57:46.781Z</t>
+          <t>2026-07-10T03:28:03.594Z</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1234,42 +1234,42 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>P023</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>José Luis</t>
+          <t>manu</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Marcelo</t>
+          <t>José Luis</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1348,50 +1348,107 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
+          <t>P015</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Marcelo</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>P019</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Omar</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1514,7 +1571,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1529,12 +1586,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>["Arthur"]</t>
+          <t>["Arthur","manu"]</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1638,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1648,7 +1705,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1720,7 +1777,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -5929,6 +5986,194 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>manu</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>QF1</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Francia vs Marruecos</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>90 minutos</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>confirmed</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>manu</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>QF2</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>España vs Bélgica</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>90 minutos</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>manu</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>QF3</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Noruega vs Inglaterra</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Noruega</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Suplementario</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>manu</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>QF4</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Argentina vs Suiza</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>1-2</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Suiza</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>90 minutos</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Pendiente</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
@@ -6188,7 +6433,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>131</t>
+          <t>149</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6445,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -6217,7 +6462,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">

--- a/docs/kinela_actualizada.xlsx
+++ b/docs/kinela_actualizada.xlsx
@@ -65,17 +65,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-10T03:28:03.594Z</t>
+          <t>2026-07-10T22:18:01.737Z</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jean</t>
+          <t>Freddy</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>99</t>
         </is>
       </c>
     </row>
@@ -151,17 +151,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>P003</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Jean</t>
+          <t>Freddy</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>99</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -171,17 +171,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -191,12 +191,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>70</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -208,37 +208,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P001</t>
+          <t>P003</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Freddy</t>
+          <t>Jean</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -248,12 +248,12 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>75</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -275,27 +275,27 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>89</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -310,7 +310,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -322,27 +322,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P006</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Anny</t>
+          <t>Diego</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -352,7 +352,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -362,12 +362,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -379,17 +379,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Diego</t>
+          <t>Gabriela</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>75</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -399,7 +399,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -409,7 +409,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -419,12 +419,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -436,17 +436,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P016</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Gabriela</t>
+          <t>Anny</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>73</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -456,17 +456,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -476,12 +476,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -493,27 +493,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jorge</t>
+          <t>Arthur</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>71</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -523,22 +523,22 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -607,17 +607,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Arthur</t>
+          <t>Jorge</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -627,32 +627,32 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -664,17 +664,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>P007</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Gino</t>
+          <t>Aldo</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -684,14 +684,14 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>1</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -721,22 +721,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P012</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aldo</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -778,17 +778,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P009</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Javier</t>
+          <t>Gino</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -798,14 +798,14 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>1</t>
@@ -818,12 +818,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -835,22 +835,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Javier</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -860,27 +860,27 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -892,17 +892,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Moisés</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -912,19 +912,19 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
@@ -932,12 +932,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P017</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Juan</t>
+          <t>Moisés</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -979,22 +979,22 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -1006,52 +1006,52 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P020</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>38</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1083,32 +1083,32 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
     </row>
@@ -1120,17 +1120,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>P012</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Juan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1140,32 +1140,32 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1177,27 +1177,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>P021</t>
+          <t>P023</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Diana</t>
+          <t>manu</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1234,52 +1234,52 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>P023</t>
+          <t>P021</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>manu</t>
+          <t>Diana</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1613,22 +1613,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>España</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>90 minutos</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["Daniel","Diego","Jesús","Freddy","Arthur"]</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>160</t>
         </is>
       </c>
     </row>
@@ -1930,17 +1930,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -2118,17 +2118,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -2306,17 +2306,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -2494,7 +2494,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -2682,17 +2682,17 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -2870,17 +2870,17 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -3246,17 +3246,17 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -3434,7 +3434,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -3998,17 +3998,17 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -4186,17 +4186,17 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -4750,17 +4750,17 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -4938,17 +4938,17 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -5126,17 +5126,17 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -5314,7 +5314,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -5502,17 +5502,17 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -5690,7 +5690,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5700,7 +5700,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -5878,17 +5878,17 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -6066,17 +6066,17 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -6411,12 +6411,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Jean</t>
+          <t>Freddy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>99</t>
         </is>
       </c>
     </row>
@@ -6428,12 +6428,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Francia vs Marruecos</t>
+          <t>España vs Bélgica</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>160</t>
         </is>
       </c>
     </row>

--- a/docs/kinela_actualizada.xlsx
+++ b/docs/kinela_actualizada.xlsx
@@ -65,7 +65,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-10T22:18:01.737Z</t>
+          <t>2026-07-12T00:04:47.860Z</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -75,7 +75,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>102</t>
         </is>
       </c>
     </row>
@@ -161,7 +161,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>102</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -171,7 +171,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -181,7 +181,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -196,7 +196,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -218,7 +218,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -238,7 +238,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -253,7 +253,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -265,17 +265,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P006</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jesús</t>
+          <t>Diego</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>92</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -295,7 +295,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -305,12 +305,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>36</t>
         </is>
       </c>
     </row>
@@ -322,17 +322,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P005</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Diego</t>
+          <t>Jesús</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>89</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -347,7 +347,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -362,12 +362,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -389,7 +389,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -409,7 +409,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -424,7 +424,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -446,7 +446,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>80</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -461,12 +461,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>78</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -518,12 +518,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>43</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -570,17 +570,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -607,52 +607,52 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P007</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jorge</t>
+          <t>Aldo</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -664,12 +664,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aldo</t>
+          <t>Jorge</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -689,27 +689,27 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -721,32 +721,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P012</t>
+          <t>P009</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Gino</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -778,37 +778,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>P012</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Gino</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P020</t>
+          <t>P022</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Óscar</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -912,17 +912,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -932,12 +932,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Moisés</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -969,12 +969,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -989,12 +989,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1006,52 +1006,52 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P017</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Moisés</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -1063,27 +1063,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>P022</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Óscar</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1093,22 +1093,22 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P023</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Juan</t>
+          <t>manu</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>36</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
     </row>
@@ -1177,52 +1177,52 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>P023</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>manu</t>
+          <t>Juan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1680,22 +1680,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Inglaterra</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Suplementario</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>81</t>
         </is>
       </c>
     </row>
@@ -1977,17 +1977,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -2165,17 +2165,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -2353,17 +2353,17 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2541,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -2917,17 +2917,17 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -3105,17 +3105,17 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -3293,17 +3293,17 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -3481,17 +3481,17 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -4045,17 +4045,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -4233,17 +4233,17 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -4421,7 +4421,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -4797,17 +4797,17 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -4985,7 +4985,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -5173,17 +5173,17 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -5737,7 +5737,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5747,7 +5747,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -5925,17 +5925,17 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -6113,17 +6113,17 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>102</t>
         </is>
       </c>
     </row>

--- a/docs/kinela_actualizada.xlsx
+++ b/docs/kinela_actualizada.xlsx
@@ -65,7 +65,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-12T00:04:47.860Z</t>
+          <t>2026-07-12T03:47:59.785Z</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -75,7 +75,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>105</t>
         </is>
       </c>
     </row>
@@ -161,7 +161,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -171,17 +171,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -196,7 +196,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>35</t>
         </is>
       </c>
     </row>
@@ -218,7 +218,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>104</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -228,17 +228,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -253,7 +253,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -275,7 +275,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>95</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -285,17 +285,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -310,7 +310,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -332,7 +332,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>92</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -342,17 +342,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -367,7 +367,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -389,7 +389,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>85</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -409,7 +409,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -424,7 +424,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -446,7 +446,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>83</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -456,7 +456,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -466,7 +466,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -481,7 +481,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -503,7 +503,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>81</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -513,17 +513,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>46</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>77</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -570,7 +570,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -580,7 +580,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -617,7 +617,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -627,7 +627,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -664,17 +664,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P012</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jorge</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -689,27 +689,27 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>63</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -778,17 +778,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P012</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Jorge</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>59</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -969,17 +969,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1026,19 +1026,19 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
@@ -1051,7 +1051,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1747,22 +1747,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>Suplementario</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>64</t>
         </is>
       </c>
     </row>
@@ -2024,17 +2024,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -2212,17 +2212,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -2400,17 +2400,17 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -2776,17 +2776,17 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -2964,17 +2964,17 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -3152,17 +3152,17 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -3340,17 +3340,17 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -3528,17 +3528,17 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3904,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -4092,17 +4092,17 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -4280,17 +4280,17 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -4656,7 +4656,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -4844,17 +4844,17 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -5032,17 +5032,17 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -5220,17 +5220,17 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -5596,17 +5596,17 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -5784,7 +5784,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -5972,17 +5972,17 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -6160,7 +6160,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Pendiente</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -6170,7 +6170,7 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>scheduled</t>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>105</t>
         </is>
       </c>
     </row>

--- a/docs/kinela_actualizada.xlsx
+++ b/docs/kinela_actualizada.xlsx
@@ -7,7 +7,8 @@
     <sheet name="Partidos" sheetId="3" r:id="rId3"/>
     <sheet name="Detalle_Participantes" sheetId="4" r:id="rId4"/>
     <sheet name="Antecedente_Octavos" sheetId="5" r:id="rId5"/>
-    <sheet name="Metricas" sheetId="6" r:id="rId6"/>
+    <sheet name="Semifinales" sheetId="6" r:id="rId6"/>
+    <sheet name="Metricas" sheetId="7" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
@@ -65,7 +66,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-12T03:47:59.785Z</t>
+          <t>2026-07-13T15:05:44.194Z</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -265,17 +266,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P006</t>
+          <t>P005</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Diego</t>
+          <t>Jesús</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>92</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -295,7 +296,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -305,12 +306,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>33</t>
         </is>
       </c>
     </row>
@@ -322,17 +323,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P005</t>
+          <t>P006</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jesús</t>
+          <t>Diego</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>88</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -347,7 +348,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -362,12 +363,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>56</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -379,37 +380,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>P002</t>
+          <t>P011</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Gabriela</t>
+          <t>Jorge</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -424,7 +425,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -436,17 +437,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P016</t>
+          <t>P018</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Anny</t>
+          <t>Alex</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>78</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -456,12 +457,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -476,12 +477,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>49</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -493,22 +494,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P013</t>
+          <t>P016</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Arthur</t>
+          <t>Anny</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>76</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -523,7 +524,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -533,12 +534,12 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -550,17 +551,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>P018</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alex</t>
+          <t>Gabriela</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>75</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -570,17 +571,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -590,12 +591,12 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>61</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -607,32 +608,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P007</t>
+          <t>P013</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aldo</t>
+          <t>Arthur</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>74</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -647,12 +648,12 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>39</t>
         </is>
       </c>
     </row>
@@ -664,27 +665,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P012</t>
+          <t>P010</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Daniel</t>
+          <t>Manuel</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -694,7 +695,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -704,12 +705,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -721,17 +722,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P009</t>
+          <t>P007</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Gino</t>
+          <t>Aldo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -741,12 +742,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -761,12 +762,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -778,12 +779,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P011</t>
+          <t>P012</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jorge</t>
+          <t>Daniel</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -803,27 +804,27 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -835,17 +836,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>P008</t>
+          <t>P022</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Javier</t>
+          <t>Óscar</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -855,12 +856,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -875,12 +876,12 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -892,12 +893,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>P022</t>
+          <t>P017</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Óscar</t>
+          <t>Moisés</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -907,12 +908,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -922,7 +923,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -932,12 +933,12 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -949,17 +950,17 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P020</t>
+          <t>P009</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Fernando</t>
+          <t>Gino</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -969,7 +970,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -979,7 +980,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -989,12 +990,12 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>42</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -1006,17 +1007,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>P017</t>
+          <t>P020</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Moisés</t>
+          <t>Fernando</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1026,12 +1027,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1046,12 +1047,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1063,52 +1064,52 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>P010</t>
+          <t>P008</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Manuel</t>
+          <t>Javier</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1121,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>P023</t>
+          <t>P004</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>manu</t>
+          <t>Juan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1135,12 +1136,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1150,22 +1151,22 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1178,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>P004</t>
+          <t>P021</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Juan</t>
+          <t>Diana</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1197,12 +1198,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1217,7 +1218,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1234,17 +1235,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>P021</t>
+          <t>P014</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Diana</t>
+          <t>José Luis</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1254,12 +1255,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1274,7 +1275,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -1291,12 +1292,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>P014</t>
+          <t>P015</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>José Luis</t>
+          <t>Marcelo</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1348,12 +1349,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>P015</t>
+          <t>P019</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Marcelo</t>
+          <t>Omar</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1392,63 +1393,6 @@
         </is>
       </c>
       <c r="K23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>P019</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Omar</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1571,7 +1515,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -1586,12 +1530,12 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>["Arthur","manu"]</t>
+          <t>["Arthur","Manuel"]</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>159</t>
         </is>
       </c>
     </row>
@@ -1638,7 +1582,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -1658,7 +1602,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>166</t>
         </is>
       </c>
     </row>
@@ -1710,7 +1654,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1725,7 +1669,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>32</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1716,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1787,12 +1731,12 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["Moisés"]</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>70</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2114,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2217,7 +2161,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2922,7 +2866,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3251,7 +3195,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3298,7 +3242,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -3486,7 +3430,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3560,17 +3504,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>90 minutos</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3580,7 +3524,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -3607,17 +3551,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>España</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>90 minutos</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -3627,7 +3571,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3654,17 +3598,17 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Suplementario</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3701,17 +3645,17 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Suiza</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>90 minutos</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3748,17 +3692,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Francia</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>90 minutos</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3768,7 +3712,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3795,17 +3739,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>España</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>90 minutos</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3815,7 +3759,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3842,17 +3786,17 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Noruega</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>90 minutos</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3889,17 +3833,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>Argentina</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Sin envio</t>
+          <t>90 minutos</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -3909,7 +3853,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4050,7 +3994,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -4238,7 +4182,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -4802,7 +4746,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4943,7 +4887,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -5037,7 +4981,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -5178,7 +5122,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -5930,7 +5874,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5981,194 +5925,6 @@
         </is>
       </c>
       <c r="I89" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>manu</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>QF1</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Francia vs Marruecos</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>Francia</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>90 minutos</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>manu</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>QF2</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>España vs Bélgica</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>España</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>90 minutos</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>2-1</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>manu</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>QF3</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Noruega vs Inglaterra</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>3-2</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Noruega</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Suplementario</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>confirmed</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>manu</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>QF4</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Argentina vs Suiza</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>1-2</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Suiza</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>90 minutos</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>3-1</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
         <is>
           <t>confirmed</t>
         </is>
@@ -6389,40 +6145,158 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>metrica</t>
+          <t>partido_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>valor</t>
+          <t>fase</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>puntos</t>
+          <t>fecha_hora_peru</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>equipo_a</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>equipo_b</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>fuente</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>estado</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Lider actual</t>
+          <t>SF1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Freddy</t>
+          <t>Semifinal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>2026-07-14T14:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Francia</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>España</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ESPN</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Programado</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>SF2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Semifinal</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>2026-07-15T14:00:00-05:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Inglaterra</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Argentina</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ESPN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Programado</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>metrica</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>puntos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Lider actual</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Freddy</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>Partido con mas puntos repartidos</t>
         </is>
       </c>
@@ -6433,7 +6307,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>166</t>
         </is>
       </c>
     </row>
@@ -6445,7 +6319,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>45</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
